--- a/output/StructureDefinition-botswana-amr-special-test-observation.xlsx
+++ b/output/StructureDefinition-botswana-amr-special-test-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2373" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2452" uniqueCount="507">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-09T10:14:37-04:00</t>
+    <t>2026-03-13T15:05:11-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Records special AMR test results (ESBL, Carbapenemase, D-Zone, MRSA) in Botswana AMR surveillance</t>
+    <t>Records special AMR test results (ESBL, Carbapenemase, D-Zone, MRSA) in Botswana AMR surveillance. Should be referenced from the parent OrganismObservation via hasMember.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}bw-amr-4:If there is no value, a dataAbsentReason must be provided {value.exists() or dataAbsentReason.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -448,7 +448,7 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.3.0)
 </t>
   </si>
   <si>
@@ -486,7 +486,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.3.0</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -507,7 +507,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.3.0</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -550,7 +550,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -672,7 +672,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.3.0|DeviceRequest|4.3.0|ImmunizationRecommendation|4.3.0|MedicationRequest|4.3.0|NutritionOrder|4.3.0|ServiceRequest|4.3.0)
 </t>
   </si>
   <si>
@@ -701,7 +701,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.3.0|MedicationDispense|4.3.0|MedicationStatement|4.3.0|Procedure|4.3.0|Immunization|4.3.0|ImagingStudy|4.3.0)
 </t>
   </si>
   <si>
@@ -766,6 +766,9 @@
   </si>
   <si>
     <t>Observation.category</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
@@ -787,13 +790,47 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.3.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
   </si>
   <si>
     <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:laboratory</t>
+  </si>
+  <si>
+    <t>laboratory</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
+    &lt;code value="laboratory"/&gt;
+    &lt;display value="Laboratory"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Observation.category:microbiologyStudies</t>
+  </si>
+  <si>
+    <t>microbiologyStudies</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="18725-2"/&gt;
+    &lt;display value="Microbiology studies (set)"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -870,7 +907,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.3.0)
 </t>
   </si>
   <si>
@@ -893,7 +930,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.3.0)
 </t>
   </si>
   <si>
@@ -993,7 +1030,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.3.0|PractitionerRole|4.3.0|Organization|4.3.0|CareTeam|4.3.0|Patient|4.3.0|RelatedPerson|4.3.0)
 </t>
   </si>
   <si>
@@ -1077,7 +1114,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.3.0</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1109,7 +1146,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.3.0</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1165,7 +1202,7 @@
     <t>SNOMED CT Body site concepts</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.3.0</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1198,7 +1235,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.3.0</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1238,7 +1275,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.3.0|DeviceMetric|4.3.0)
 </t>
   </si>
   <si>
@@ -1322,7 +1359,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.3.0}
 </t>
   </si>
   <si>
@@ -1372,7 +1409,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.3.0</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1405,7 +1442,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.3.0</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1442,7 +1479,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(Observation|4.3.0|QuestionnaireResponse|4.3.0|MolecularSequence|4.3.0)
 </t>
   </si>
   <si>
@@ -1464,7 +1501,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.3.0|ImagingStudy|4.3.0|Media|4.3.0|QuestionnaireResponse|4.3.0|Observation|4.3.0|MolecularSequence|4.3.0)
 </t>
   </si>
   <si>
@@ -1529,7 +1566,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.3.0</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -1876,7 +1913,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP61"/>
+  <dimension ref="A1:AP63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.046875" customWidth="true" bestFit="true"/>
@@ -1889,7 +1926,7 @@
     <col min="8" max="8" width="13.609375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.1796875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="102.26953125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="131.671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4579,7 +4616,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>242</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>81</v>
@@ -4594,19 +4631,19 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4634,25 +4671,23 @@
         <v>171</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>241</v>
@@ -4679,10 +4714,10 @@
         <v>20</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>20</v>
@@ -4690,14 +4725,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="D24" t="s" s="2">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4713,22 +4750,22 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4738,7 +4775,7 @@
         <v>20</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>20</v>
@@ -4753,11 +4790,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4775,13 +4814,13 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
@@ -4790,32 +4829,34 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>258</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>259</v>
+        <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>263</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4833,22 +4874,22 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4858,7 +4899,7 @@
         <v>20</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>20</v>
+        <v>258</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>20</v>
@@ -4873,13 +4914,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>20</v>
+        <v>248</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>20</v>
+        <v>249</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4897,13 +4938,13 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
@@ -4912,19 +4953,19 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>271</v>
+        <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>20</v>
@@ -4932,21 +4973,21 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4958,18 +4999,20 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
       </c>
@@ -4993,13 +5036,11 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>20</v>
+        <v>265</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -5017,13 +5058,13 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
@@ -5032,38 +5073,38 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>20</v>
+        <v>266</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>20</v>
+        <v>271</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>281</v>
+        <v>20</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>93</v>
@@ -5078,19 +5119,19 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5139,7 +5180,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5154,19 +5195,19 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>20</v>
@@ -5174,21 +5215,21 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>292</v>
+        <v>20</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -5200,20 +5241,18 @@
         <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -5249,23 +5288,25 @@
         <v>20</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AC28" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>299</v>
+        <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
@@ -5274,19 +5315,19 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>301</v>
+        <v>268</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>303</v>
+        <v>281</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>20</v>
@@ -5294,20 +5335,18 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>93</v>
@@ -5322,19 +5361,19 @@
         <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5383,7 +5422,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5398,19 +5437,19 @@
         <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>20</v>
@@ -5418,18 +5457,18 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>93</v>
@@ -5444,18 +5483,20 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>128</v>
+        <v>301</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
@@ -5491,19 +5532,17 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>20</v>
+        <v>307</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5518,19 +5557,19 @@
         <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>20</v>
+        <v>308</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>20</v>
@@ -5538,21 +5577,23 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C31" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="B31" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5564,17 +5605,19 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="O31" t="s" s="2">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5623,13 +5666,13 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
@@ -5638,19 +5681,19 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>20</v>
@@ -5658,10 +5701,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5669,7 +5712,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>93</v>
@@ -5684,20 +5727,18 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>242</v>
+        <v>128</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
@@ -5733,17 +5774,19 @@
         <v>20</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>299</v>
+        <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5752,7 +5795,7 @@
         <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>327</v>
+        <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>105</v>
@@ -5761,40 +5804,38 @@
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>328</v>
+        <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5806,7 +5847,7 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>242</v>
+        <v>322</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>323</v>
@@ -5814,11 +5855,9 @@
       <c r="M33" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5843,11 +5882,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>334</v>
+        <v>20</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5865,45 +5906,45 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>327</v>
+        <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>20</v>
+        <v>326</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AN33" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AP33" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5911,7 +5952,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>93</v>
@@ -5923,22 +5964,22 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5963,31 +6004,29 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>340</v>
+        <v>20</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>341</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>20</v>
+        <v>307</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5996,7 +6035,7 @@
         <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>105</v>
@@ -6005,38 +6044,40 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>20</v>
+        <v>336</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>191</v>
+        <v>337</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>20</v>
+        <v>339</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="D35" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -6045,22 +6086,22 @@
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6085,13 +6126,11 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -6109,16 +6148,16 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>20</v>
+        <v>335</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>105</v>
@@ -6127,27 +6166,27 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>355</v>
+        <v>339</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6158,7 +6197,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -6170,19 +6209,19 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>357</v>
+        <v>243</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6207,13 +6246,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>20</v>
+        <v>348</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>20</v>
+        <v>349</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -6231,16 +6270,16 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>20</v>
+        <v>350</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>105</v>
@@ -6252,10 +6291,10 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>362</v>
+        <v>191</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6266,21 +6305,21 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>20</v>
+        <v>353</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6292,18 +6331,20 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
@@ -6327,13 +6368,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -6351,13 +6392,13 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
@@ -6369,27 +6410,27 @@
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6400,7 +6441,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6412,19 +6453,19 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>242</v>
+        <v>365</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6449,13 +6490,13 @@
         <v>20</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>380</v>
+        <v>20</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>20</v>
@@ -6473,13 +6514,13 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
@@ -6494,10 +6535,10 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6508,10 +6549,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6519,7 +6560,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
@@ -6534,16 +6575,16 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>384</v>
+        <v>243</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6569,13 +6610,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>20</v>
+        <v>376</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>20</v>
+        <v>377</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6593,7 +6634,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6611,27 +6652,27 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>391</v>
+        <v>381</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6654,18 +6695,20 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>393</v>
+        <v>243</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6689,13 +6732,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>20</v>
+        <v>387</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>20</v>
+        <v>388</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6713,7 +6756,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6731,27 +6774,27 @@
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>397</v>
+        <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>400</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6759,10 +6802,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6774,20 +6817,18 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
       </c>
@@ -6835,45 +6876,45 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>407</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>20</v>
+        <v>396</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>20</v>
+        <v>399</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6896,15 +6937,17 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>107</v>
+        <v>402</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -6953,7 +6996,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>109</v>
+        <v>400</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6965,37 +7008,37 @@
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>20</v>
+        <v>405</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>20</v>
+        <v>406</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>110</v>
+        <v>407</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>20</v>
+        <v>408</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7014,18 +7057,20 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>113</v>
+        <v>410</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>114</v>
+        <v>411</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>115</v>
+        <v>412</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
       </c>
@@ -7073,7 +7118,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>120</v>
+        <v>409</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7085,7 +7130,7 @@
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>121</v>
+        <v>415</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -7094,10 +7139,10 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>20</v>
+        <v>416</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>110</v>
+        <v>417</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -7108,46 +7153,42 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>414</v>
+        <v>20</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>113</v>
+        <v>419</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>415</v>
+        <v>107</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>20</v>
       </c>
@@ -7195,19 +7236,19 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>417</v>
+        <v>109</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -7219,7 +7260,7 @@
         <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>191</v>
+        <v>110</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
@@ -7230,21 +7271,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -7256,15 +7297,17 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>419</v>
+        <v>113</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>420</v>
+        <v>114</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>116</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7313,19 +7356,19 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>418</v>
+        <v>120</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>422</v>
+        <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -7334,10 +7377,10 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>423</v>
+        <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>424</v>
+        <v>110</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7348,42 +7391,46 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>20</v>
+        <v>422</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>419</v>
+        <v>113</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
       </c>
@@ -7437,13 +7484,13 @@
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>422</v>
+        <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
@@ -7452,10 +7499,10 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>423</v>
+        <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>428</v>
+        <v>191</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7466,10 +7513,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7492,20 +7539,16 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>242</v>
+        <v>427</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
       </c>
@@ -7529,13 +7572,13 @@
         <v>20</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>434</v>
+        <v>20</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>435</v>
+        <v>20</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7553,7 +7596,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7562,7 +7605,7 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>20</v>
+        <v>430</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>105</v>
@@ -7571,13 +7614,13 @@
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>436</v>
+        <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>354</v>
+        <v>432</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -7588,10 +7631,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7602,7 +7645,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7614,20 +7657,16 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>242</v>
+        <v>427</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>442</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -7651,13 +7690,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>443</v>
+        <v>20</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>444</v>
+        <v>20</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7675,16 +7714,16 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>20</v>
+        <v>430</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>105</v>
@@ -7693,13 +7732,13 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -7710,10 +7749,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7736,17 +7775,19 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>446</v>
+        <v>243</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7771,13 +7812,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>20</v>
+        <v>442</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>20</v>
+        <v>443</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7795,7 +7836,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7813,13 +7854,13 @@
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>20</v>
+        <v>444</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>20</v>
+        <v>445</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>450</v>
+        <v>362</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -7830,10 +7871,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7844,7 +7885,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -7856,16 +7897,20 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>411</v>
+        <v>243</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
       </c>
@@ -7889,13 +7934,13 @@
         <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>20</v>
+        <v>451</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>20</v>
+        <v>452</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -7913,13 +7958,13 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
@@ -7931,13 +7976,13 @@
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>20</v>
+        <v>444</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>454</v>
+        <v>362</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
@@ -7948,10 +7993,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7962,7 +8007,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -7971,21 +8016,21 @@
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="N51" s="2"/>
+      <c r="O51" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>20</v>
       </c>
@@ -8033,13 +8078,13 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
@@ -8054,10 +8099,10 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>460</v>
+        <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -8068,10 +8113,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8082,7 +8127,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -8091,20 +8136,18 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8153,13 +8196,13 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
@@ -8174,10 +8217,10 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>460</v>
+        <v>431</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8188,10 +8231,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8214,20 +8257,18 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>402</v>
+        <v>464</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
       </c>
@@ -8275,7 +8316,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8287,7 +8328,7 @@
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>473</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
@@ -8296,10 +8337,10 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8310,10 +8351,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8324,7 +8365,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8333,18 +8374,20 @@
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>411</v>
+        <v>471</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>107</v>
+        <v>472</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8393,19 +8436,19 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>109</v>
+        <v>470</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
@@ -8414,10 +8457,10 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>20</v>
+        <v>468</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>110</v>
+        <v>475</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
@@ -8428,14 +8471,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8451,21 +8494,23 @@
         <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>113</v>
+        <v>410</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>114</v>
+        <v>477</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>115</v>
+        <v>478</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>480</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
       </c>
@@ -8513,7 +8558,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>120</v>
+        <v>476</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8525,7 +8570,7 @@
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>121</v>
+        <v>481</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -8534,10 +8579,10 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>20</v>
+        <v>482</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>110</v>
+        <v>483</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -8548,46 +8593,42 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>414</v>
+        <v>20</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>113</v>
+        <v>419</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>415</v>
+        <v>107</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>20</v>
       </c>
@@ -8635,19 +8676,19 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>417</v>
+        <v>109</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8659,7 +8700,7 @@
         <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>191</v>
+        <v>110</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -8670,21 +8711,21 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8693,23 +8734,21 @@
         <v>20</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>480</v>
+        <v>114</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>481</v>
+        <v>115</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>20</v>
       </c>
@@ -8733,13 +8772,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>483</v>
+        <v>20</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>484</v>
+        <v>20</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -8757,34 +8796,34 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>479</v>
+        <v>120</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>485</v>
+        <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>261</v>
+        <v>110</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>262</v>
+        <v>20</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>20</v>
@@ -8799,38 +8838,38 @@
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>20</v>
+        <v>422</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>487</v>
+        <v>113</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>488</v>
+        <v>423</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>324</v>
+        <v>424</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>489</v>
+        <v>116</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>326</v>
+        <v>198</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -8879,45 +8918,45 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>486</v>
+        <v>425</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>490</v>
+        <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>329</v>
+        <v>20</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>330</v>
+        <v>191</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8925,7 +8964,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>93</v>
@@ -8937,22 +8976,22 @@
         <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>339</v>
+        <v>264</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -8977,13 +9016,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>340</v>
+        <v>491</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>341</v>
+        <v>492</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -9001,16 +9040,16 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>342</v>
+        <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
@@ -9019,16 +9058,16 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>20</v>
+        <v>493</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>191</v>
+        <v>268</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>343</v>
+        <v>269</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>20</v>
+        <v>270</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>20</v>
@@ -9036,21 +9075,21 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -9059,22 +9098,22 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>242</v>
+        <v>495</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>346</v>
+        <v>496</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>348</v>
+        <v>497</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9099,13 +9138,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>351</v>
+        <v>20</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9123,13 +9162,13 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
@@ -9141,27 +9180,27 @@
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>352</v>
+        <v>498</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>355</v>
+        <v>339</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9172,7 +9211,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -9184,19 +9223,19 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>82</v>
+        <v>243</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>405</v>
+        <v>502</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>406</v>
+        <v>347</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9221,13 +9260,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>20</v>
+        <v>348</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>20</v>
+        <v>349</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -9245,16 +9284,16 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>20</v>
+        <v>350</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
@@ -9266,15 +9305,259 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>408</v>
+        <v>191</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>409</v>
+        <v>351</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP61" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>20</v>
       </c>
     </row>

--- a/output/StructureDefinition-botswana-amr-special-test-observation.xlsx
+++ b/output/StructureDefinition-botswana-amr-special-test-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2452" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2151" uniqueCount="468">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/StructureDefinition/botswana-amr-special-test-observation</t>
+    <t>http://bw.health.gov/fhir/amr/StructureDefinition/botswana-amr-special-test-observation</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:05:11-04:00</t>
+    <t>2026-03-13T21:27:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -339,22 +339,110 @@
 </t>
   </si>
   <si>
-    <t>Observation.meta.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Observation.meta.extension</t>
+    <t>Observation.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>Observation.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>IETF language tag</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>Observation.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>Observation.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Observation.extension</t>
   </si>
   <si>
     <t>extensions
@@ -368,259 +456,19 @@
     <t>Additional content defined by implementations</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
+    <t>DomainResource.extension</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Observation.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>Observation.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4B/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>Observation.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>Observation.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.3.0)
-</t>
-  </si>
-  <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>http://bw.health.gov/fhir/StructureDefinition/BotswanaAMR-SpecialTestObservation</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>Observation.meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.3.0</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>Observation.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.3.0</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>Observation.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>Observation.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>IETF language tag</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>Observation.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>Observation.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Observation.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
     <t>Observation.modifierExtension</t>
   </si>
   <si>
@@ -795,6 +643,9 @@
   <si>
     <t xml:space="preserve">pattern:$this}
 </t>
+  </si>
+  <si>
+    <t>open</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -852,7 +703,7 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/ValueSet/botswana-amr-special-test-vs</t>
+    <t>http://bw.health.gov/fhir/amr/ValueSet/botswana-amr-special-test-vs</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1009,6 +860,10 @@
     <t>Observation.issued</t>
   </si>
   <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
     <t>Date/Time this version was made available</t>
   </si>
   <si>
@@ -1092,7 +947,7 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
-    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/ValueSet/botswana-amr-test-result-status-vs</t>
+    <t>http://bw.health.gov/fhir/amr/ValueSet/botswana-amr-test-result-status-vs</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -1111,6 +966,9 @@
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
@@ -1199,6 +1057,9 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
   </si>
   <si>
+    <t>example</t>
+  </si>
+  <si>
     <t>SNOMED CT Body site concepts</t>
   </si>
   <si>
@@ -1247,7 +1108,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/StructureDefinition/botswana-amr-specimen)
+    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/amr/StructureDefinition/botswana-amr-specimen)
 </t>
   </si>
   <si>
@@ -1336,7 +1197,25 @@
 </t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Observation.referenceRange.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
   </si>
   <si>
     <t>Observation.referenceRange.modifierExtension</t>
@@ -1913,7 +1792,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP63"/>
+  <dimension ref="A1:AP55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.046875" customWidth="true" bestFit="true"/>
@@ -1941,10 +1820,10 @@
     <col min="23" max="23" width="16.40625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="15.85546875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="55.359375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="86.21484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.32421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.2734375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.1171875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.56640625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.16015625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.3671875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="11.84375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="36.79296875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2467,21 +2346,23 @@
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N5" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="N5" t="s" s="2">
+        <v>110</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>20</v>
@@ -2530,7 +2411,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -2542,7 +2423,7 @@
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2554,7 +2435,7 @@
         <v>20</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>20</v>
@@ -2565,21 +2446,21 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2626,28 +2507,28 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>120</v>
@@ -2656,13 +2537,13 @@
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2674,7 +2555,7 @@
         <v>20</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>20</v>
@@ -2685,14 +2566,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2708,19 +2589,19 @@
         <v>20</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2770,7 +2651,7 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -2794,7 +2675,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>20</v>
+        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>20</v>
@@ -2805,21 +2686,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2828,19 +2709,19 @@
         <v>20</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2890,19 +2771,19 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>20</v>
@@ -2914,7 +2795,7 @@
         <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>20</v>
@@ -2925,21 +2806,21 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2948,19 +2829,19 @@
         <v>20</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3010,19 +2891,19 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -3034,7 +2915,7 @@
         <v>20</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>20</v>
@@ -3045,14 +2926,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3065,24 +2946,26 @@
         <v>20</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O10" s="2"/>
+      <c r="O10" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P10" t="s" s="2">
         <v>20</v>
       </c>
@@ -3091,7 +2974,7 @@
         <v>20</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="T10" t="s" s="2">
         <v>20</v>
@@ -3130,7 +3013,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3142,7 +3025,7 @@
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -3154,7 +3037,7 @@
         <v>20</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>20</v>
@@ -3165,10 +3048,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3191,18 +3074,18 @@
         <v>94</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O11" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
       </c>
@@ -3226,29 +3109,31 @@
         <v>20</v>
       </c>
       <c r="X11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF11" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="Y11" s="2"/>
-      <c r="Z11" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3263,19 +3148,19 @@
         <v>105</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>20</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>20</v>
+        <v>159</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>20</v>
@@ -3283,14 +3168,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3309,18 +3194,18 @@
         <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O12" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
       </c>
@@ -3344,11 +3229,13 @@
         <v>20</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="Y12" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z12" t="s" s="2">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>20</v>
@@ -3381,16 +3268,16 @@
         <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>20</v>
@@ -3401,42 +3288,42 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3486,13 +3373,13 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
@@ -3501,16 +3388,16 @@
         <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>20</v>
@@ -3521,10 +3408,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3532,7 +3419,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>93</v>
@@ -3541,24 +3428,26 @@
         <v>20</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>113</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O14" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
       </c>
@@ -3567,7 +3456,7 @@
         <v>20</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>20</v>
@@ -3582,13 +3471,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3606,10 +3495,10 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>93</v>
@@ -3621,19 +3510,19 @@
         <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>20</v>
@@ -3641,21 +3530,21 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3667,18 +3556,20 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O15" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
       </c>
@@ -3702,37 +3593,35 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
@@ -3750,10 +3639,10 @@
         <v>20</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>20</v>
@@ -3761,21 +3650,23 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -3787,18 +3678,20 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
       </c>
@@ -3807,7 +3700,7 @@
         <v>20</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>20</v>
@@ -3822,13 +3715,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3846,7 +3739,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3858,7 +3751,7 @@
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>190</v>
+        <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
@@ -3870,10 +3763,10 @@
         <v>20</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>20</v>
@@ -3881,21 +3774,23 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="C17" s="2"/>
+      <c r="C17" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="D17" t="s" s="2">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3907,18 +3802,20 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>113</v>
+        <v>194</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>114</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
       </c>
@@ -3927,7 +3824,7 @@
         <v>20</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>20</v>
+        <v>210</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>20</v>
@@ -3942,13 +3839,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -3966,7 +3863,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3978,7 +3875,7 @@
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
@@ -3990,10 +3887,10 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>20</v>
@@ -4001,45 +3898,45 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>112</v>
+        <v>212</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J18" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="J18" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="K18" t="s" s="2">
-        <v>113</v>
+        <v>194</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>116</v>
+        <v>215</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -4064,13 +3961,11 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>20</v>
+        <v>217</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -4088,45 +3983,45 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>20</v>
+        <v>218</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>20</v>
+        <v>219</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>20</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4134,10 +4029,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -4149,17 +4044,19 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="O19" t="s" s="2">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4208,13 +4105,13 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -4223,19 +4120,19 @@
         <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>20</v>
@@ -4243,14 +4140,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>210</v>
+        <v>20</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4269,18 +4166,18 @@
         <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>20</v>
       </c>
@@ -4328,7 +4225,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4343,19 +4240,19 @@
         <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>20</v>
@@ -4363,21 +4260,21 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4389,18 +4286,20 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
       </c>
@@ -4448,13 +4347,13 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
@@ -4463,19 +4362,19 @@
         <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>20</v>
@@ -4483,14 +4382,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>20</v>
+        <v>252</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4503,25 +4402,25 @@
         <v>20</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>167</v>
+        <v>253</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4531,7 +4430,7 @@
         <v>20</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>20</v>
@@ -4546,34 +4445,32 @@
         <v>20</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>233</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>20</v>
+        <v>259</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>93</v>
@@ -4585,19 +4482,19 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>20</v>
@@ -4605,21 +4502,23 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>20</v>
+        <v>252</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>242</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4628,22 +4527,22 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4668,35 +4567,37 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>248</v>
+        <v>20</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AC23" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
@@ -4705,19 +4606,19 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>20</v>
@@ -4725,20 +4626,18 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>93</v>
@@ -4750,23 +4649,21 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>20</v>
       </c>
@@ -4775,7 +4672,7 @@
         <v>20</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>20</v>
@@ -4790,13 +4687,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>248</v>
+        <v>20</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4814,13 +4711,13 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
@@ -4835,13 +4732,13 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>20</v>
+        <v>271</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>20</v>
@@ -4849,23 +4746,21 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4874,22 +4769,20 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4899,7 +4792,7 @@
         <v>20</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>258</v>
+        <v>20</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>20</v>
@@ -4914,13 +4807,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>248</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4938,7 +4831,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>241</v>
+        <v>274</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4953,19 +4846,19 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>20</v>
+        <v>279</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>20</v>
@@ -4973,14 +4866,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4999,19 +4892,19 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>243</v>
+        <v>194</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5036,69 +4929,71 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>265</v>
+        <v>20</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>20</v>
+        <v>259</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>20</v>
+        <v>288</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>266</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>271</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>20</v>
       </c>
@@ -5119,19 +5014,19 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>273</v>
+        <v>194</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5156,13 +5051,11 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>20</v>
+        <v>295</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -5180,7 +5073,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5189,36 +5082,36 @@
         <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>20</v>
+        <v>288</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>278</v>
+        <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>281</v>
+        <v>20</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>20</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5229,7 +5122,7 @@
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -5238,21 +5131,23 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>283</v>
+        <v>194</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -5276,13 +5171,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>20</v>
+        <v>301</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5300,16 +5195,16 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>20</v>
+        <v>304</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>105</v>
@@ -5321,13 +5216,13 @@
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>268</v>
+        <v>137</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>281</v>
+        <v>20</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>20</v>
@@ -5335,21 +5230,21 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5358,22 +5253,22 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>290</v>
+        <v>194</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5398,13 +5293,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>20</v>
+        <v>301</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>20</v>
+        <v>312</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>20</v>
+        <v>313</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5422,13 +5317,13 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
@@ -5437,41 +5332,41 @@
         <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>295</v>
+        <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>20</v>
+        <v>314</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>298</v>
+        <v>20</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>20</v>
+        <v>317</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5480,22 +5375,22 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5532,23 +5427,25 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AC30" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>307</v>
+        <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
@@ -5557,19 +5454,19 @@
         <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>308</v>
+        <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>20</v>
@@ -5577,20 +5474,18 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>93</v>
@@ -5602,23 +5497,21 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>301</v>
+        <v>194</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5642,13 +5535,13 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>20</v>
+        <v>330</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>20</v>
+        <v>331</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>20</v>
+        <v>332</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5666,7 +5559,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>299</v>
+        <v>326</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5681,30 +5574,30 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>308</v>
+        <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>20</v>
+        <v>336</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5724,21 +5617,23 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>128</v>
+        <v>194</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
@@ -5762,13 +5657,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>20</v>
+        <v>330</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>20</v>
+        <v>342</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>20</v>
+        <v>343</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -5786,7 +5681,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5807,13 +5702,13 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>320</v>
+        <v>20</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>20</v>
@@ -5821,10 +5716,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5832,10 +5727,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5844,21 +5739,21 @@
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5906,13 +5801,13 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
@@ -5921,30 +5816,30 @@
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>326</v>
+        <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>20</v>
+        <v>351</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>329</v>
+        <v>20</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>20</v>
+        <v>354</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5952,7 +5847,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>93</v>
@@ -5964,23 +5859,21 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>243</v>
+        <v>356</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -6016,17 +5909,19 @@
         <v>20</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AC34" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>307</v>
+        <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6035,7 +5930,7 @@
         <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>335</v>
+        <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>105</v>
@@ -6044,40 +5939,38 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>339</v>
+        <v>363</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -6086,22 +5979,22 @@
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>243</v>
+        <v>365</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>331</v>
+        <v>366</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>332</v>
+        <v>367</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>333</v>
+        <v>368</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>334</v>
+        <v>369</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6126,11 +6019,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>342</v>
+        <v>20</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -6148,45 +6043,45 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>335</v>
+        <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>105</v>
+        <v>370</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>337</v>
+        <v>371</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>338</v>
+        <v>372</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>339</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6209,20 +6104,16 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>243</v>
+        <v>374</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>344</v>
+        <v>375</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>20</v>
       </c>
@@ -6246,13 +6137,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>348</v>
+        <v>20</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>349</v>
+        <v>20</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -6270,7 +6161,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>343</v>
+        <v>377</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6279,10 +6170,10 @@
         <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -6291,10 +6182,10 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>191</v>
+        <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6305,14 +6196,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>353</v>
+        <v>139</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6331,20 +6222,18 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>354</v>
+        <v>141</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
@@ -6368,13 +6257,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>358</v>
+        <v>20</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>359</v>
+        <v>20</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -6392,7 +6281,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>352</v>
+        <v>381</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6404,37 +6293,37 @@
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>360</v>
+        <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>363</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>20</v>
+        <v>383</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6447,25 +6336,25 @@
         <v>20</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>365</v>
+        <v>140</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>368</v>
+        <v>143</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>369</v>
+        <v>149</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6514,7 +6403,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6526,7 +6415,7 @@
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -6535,10 +6424,10 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>370</v>
+        <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>371</v>
+        <v>137</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6549,10 +6438,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6575,17 +6464,15 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>243</v>
+        <v>388</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6610,13 +6497,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>376</v>
+        <v>20</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>377</v>
+        <v>20</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6634,7 +6521,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6643,7 +6530,7 @@
         <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>20</v>
+        <v>391</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>105</v>
@@ -6652,27 +6539,27 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>378</v>
+        <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>381</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6695,20 +6582,16 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>243</v>
+        <v>388</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6732,13 +6615,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>387</v>
+        <v>20</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>388</v>
+        <v>20</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6756,7 +6639,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6765,7 +6648,7 @@
         <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>20</v>
+        <v>391</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>105</v>
@@ -6777,10 +6660,10 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -6791,10 +6674,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6802,7 +6685,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>93</v>
@@ -6817,18 +6700,20 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>392</v>
+        <v>194</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
       </c>
@@ -6852,13 +6737,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>20</v>
+        <v>403</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>20</v>
+        <v>404</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6876,7 +6761,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6894,27 +6779,27 @@
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>398</v>
+        <v>316</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>399</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6925,7 +6810,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -6937,18 +6822,20 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>401</v>
+        <v>194</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6972,13 +6859,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>20</v>
+        <v>330</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>20</v>
+        <v>412</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>20</v>
+        <v>413</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6996,13 +6883,13 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
@@ -7020,21 +6907,21 @@
         <v>406</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>407</v>
+        <v>316</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>408</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7045,7 +6932,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -7057,19 +6944,17 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7118,19 +7003,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>415</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -7139,10 +7024,10 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>416</v>
+        <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -7153,10 +7038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7179,13 +7064,13 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>419</v>
+        <v>374</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>107</v>
+        <v>421</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>108</v>
+        <v>422</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7236,7 +7121,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>109</v>
+        <v>420</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7248,7 +7133,7 @@
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -7257,10 +7142,10 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>20</v>
+        <v>392</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>110</v>
+        <v>423</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
@@ -7271,14 +7156,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7294,19 +7179,19 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>113</v>
+        <v>425</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>114</v>
+        <v>426</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>115</v>
+        <v>427</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>116</v>
+        <v>428</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7356,7 +7241,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>120</v>
+        <v>424</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7368,7 +7253,7 @@
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -7377,10 +7262,10 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>20</v>
+        <v>429</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>110</v>
+        <v>430</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7391,14 +7276,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>422</v>
+        <v>20</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7411,26 +7296,24 @@
         <v>20</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>113</v>
+        <v>432</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>20</v>
       </c>
@@ -7478,7 +7361,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7490,7 +7373,7 @@
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
@@ -7499,10 +7382,10 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>20</v>
+        <v>429</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>191</v>
+        <v>436</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7513,10 +7396,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7527,7 +7410,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7536,19 +7419,23 @@
         <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>427</v>
+        <v>365</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
       </c>
@@ -7596,19 +7483,19 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>430</v>
+        <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>442</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -7617,10 +7504,10 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -7631,10 +7518,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7657,13 +7544,13 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>427</v>
+        <v>374</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>434</v>
+        <v>375</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>435</v>
+        <v>376</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7714,7 +7601,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>433</v>
+        <v>377</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7723,10 +7610,10 @@
         <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>430</v>
+        <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
@@ -7735,10 +7622,10 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>431</v>
+        <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>436</v>
+        <v>378</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -7749,21 +7636,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7775,20 +7662,18 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>438</v>
+        <v>141</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>439</v>
+        <v>380</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
       </c>
@@ -7812,13 +7697,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>442</v>
+        <v>20</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>443</v>
+        <v>20</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7836,31 +7721,31 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>437</v>
+        <v>381</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>444</v>
+        <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -7871,14 +7756,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>20</v>
+        <v>383</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7891,25 +7776,25 @@
         <v>20</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>447</v>
+        <v>384</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>448</v>
+        <v>385</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>449</v>
+        <v>143</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>450</v>
+        <v>149</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7934,13 +7819,13 @@
         <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>451</v>
+        <v>20</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>452</v>
+        <v>20</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -7958,7 +7843,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>446</v>
+        <v>386</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7970,19 +7855,19 @@
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>444</v>
+        <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>362</v>
+        <v>137</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
@@ -7993,10 +7878,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8004,7 +7889,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>93</v>
@@ -8016,20 +7901,22 @@
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>454</v>
+        <v>194</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="O51" t="s" s="2">
-        <v>457</v>
+        <v>216</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8054,13 +7941,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>20</v>
+        <v>330</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>20</v>
+        <v>452</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>20</v>
+        <v>453</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -8078,10 +7965,10 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>93</v>
@@ -8096,16 +7983,16 @@
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>20</v>
+        <v>454</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>458</v>
+        <v>221</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>20</v>
@@ -8113,10 +8000,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8136,19 +8023,23 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>419</v>
+        <v>456</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
       </c>
@@ -8196,7 +8087,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8214,27 +8105,27 @@
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>20</v>
+        <v>459</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>431</v>
+        <v>290</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>462</v>
+        <v>291</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>20</v>
+        <v>292</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8245,7 +8136,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -8254,21 +8145,23 @@
         <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>464</v>
+        <v>194</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>463</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
       </c>
@@ -8292,13 +8185,13 @@
         <v>20</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>20</v>
+        <v>301</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -8316,16 +8209,16 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>20</v>
+        <v>304</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>105</v>
@@ -8337,10 +8230,10 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>468</v>
+        <v>137</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>469</v>
+        <v>305</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8351,14 +8244,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>20</v>
+        <v>307</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8374,21 +8267,23 @@
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>471</v>
+        <v>194</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>472</v>
+        <v>308</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>473</v>
+        <v>309</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
       </c>
@@ -8412,13 +8307,13 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>20</v>
+        <v>301</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>20</v>
+        <v>312</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>20</v>
+        <v>313</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -8436,7 +8331,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8454,27 +8349,27 @@
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>20</v>
+        <v>314</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>468</v>
+        <v>315</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>475</v>
+        <v>316</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>20</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8494,22 +8389,22 @@
         <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>479</v>
+        <v>368</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>480</v>
+        <v>369</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8558,7 +8453,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8570,7 +8465,7 @@
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>481</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -8579,985 +8474,15 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>482</v>
+        <v>371</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>483</v>
+        <v>372</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O57" s="2"/>
-      <c r="P57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="P58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="P60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="P61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="P62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP63" t="s" s="2">
         <v>20</v>
       </c>
     </row>
